--- a/쌤워크_피드백_서식_v3.xlsx
+++ b/쌤워크_피드백_서식_v3.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="자동검수결과(1000건)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="문제보고" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="문장검수" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="스트레스(10만건)요약" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="자동검수결과(1000건)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="문제보고" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문장검수" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -127,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,6 +150,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -602,6 +607,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>대량 스트레스/안정성 점검 — 100,000건 (규칙 엔진 관찰일지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>검사 일시</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29T06:27:15.231Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>처리 건수</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>100,000건</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>오류 / 빈결과</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>0 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>소요 시간</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>150.8초 (건당 1.508ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>관찰일지 평균</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>87.01 (최저 83, 최고 96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>아이 발화 보존</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>20,001 / 20,001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>점수 분포</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>구간</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>비율</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>&lt;80</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>80-84</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>34998</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>85-89</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>47143</v>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>90-94</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>16430</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>16.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>95-100</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1429</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>영역별 관찰 평균</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>영역</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>생활습관</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>84.59999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>신체</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>84.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>예술</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>85.40000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>또래</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>자연탐구</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>놀이</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>88.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>정서</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>88.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>의사소통</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>89.09999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>최저 점수 예시(상위 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>점수</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>생성된 관찰일지</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>서연이가 큰 블록으로 자기 키만 한 탑을 완성했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>도윤이가 낮잠 시간에 스스로 이불을 덮고 누웠다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>시우가 간식 시간에 친구에게 자리를 양보했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>연우가 두 발을 번갈아 계단을 올랐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>지호가 퍼즐을 끝까지 맞추고 "다 했다!"라고 외쳤다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>건우가 사용한 컵을 정해진 자리에 가져다 두었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>지우가 그림물감으로 손바닥을 찍어 도화지를 꾸몄다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>민준이가 가을 낙엽을 모아 크기 순서대로 늘어놓았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>예린이가 양발 모아 제자리에서 여러 번 폴짝 뛰었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>주아가 신발을 바르게 신고 신발장에 정리했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>서윤이가 친구에게 양보한 뒤 뿌듯한 표정을 지었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>소율이가 블록이 부족한 친구에게 자기 것을 나눠 주었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>지우가 자기 가방을 사물함에 스스로 넣었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>서연이가 씨앗을 화분에 심고 물을 주며 돌보았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>예린이가 간식을 받고 "고맙습니다"라고 인사했다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1009"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -41717,7 +42187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42684,7 +43154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
